--- a/artfynd/A 61009-2021 artfynd.xlsx
+++ b/artfynd/A 61009-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117664470</v>
+        <v>117666782</v>
       </c>
       <c r="B2" t="n">
-        <v>97754</v>
+        <v>57169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223591</v>
+        <v>100011</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762765</v>
+        <v>762791</v>
       </c>
       <c r="R2" t="n">
-        <v>7308648</v>
+        <v>7308597</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -748,40 +760,49 @@
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117664457</v>
+        <v>117664449</v>
       </c>
       <c r="B3" t="n">
-        <v>56499</v>
+        <v>90425</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,42 +811,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>3242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762798</v>
+        <v>762801</v>
       </c>
       <c r="R3" t="n">
-        <v>7308440</v>
+        <v>7308448</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -860,11 +877,6 @@
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -882,17 +894,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117666782</v>
+        <v>117664470</v>
       </c>
       <c r="B4" t="n">
-        <v>57169</v>
+        <v>97754</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,50 +913,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100011</v>
+        <v>223591</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762791</v>
+        <v>762765</v>
       </c>
       <c r="R4" t="n">
-        <v>7308597</v>
+        <v>7308648</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,49 +974,40 @@
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117664449</v>
+        <v>117664457</v>
       </c>
       <c r="B5" t="n">
-        <v>90425</v>
+        <v>56499</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,38 +1016,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3242</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762801</v>
+        <v>762798</v>
       </c>
       <c r="R5" t="n">
-        <v>7308448</v>
+        <v>7308440</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1091,6 +1086,11 @@
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 61009-2021 artfynd.xlsx
+++ b/artfynd/A 61009-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117666782</v>
+        <v>117664449</v>
       </c>
       <c r="B2" t="n">
-        <v>57169</v>
+        <v>90427</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100011</v>
+        <v>3242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762791</v>
+        <v>762801</v>
       </c>
       <c r="R2" t="n">
-        <v>7308597</v>
+        <v>7308448</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -760,19 +748,9 @@
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117664449</v>
+        <v>117664470</v>
       </c>
       <c r="B3" t="n">
-        <v>90425</v>
+        <v>97756</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3242</v>
+        <v>223591</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762801</v>
+        <v>762765</v>
       </c>
       <c r="R3" t="n">
-        <v>7308448</v>
+        <v>7308648</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -883,6 +861,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -901,10 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117664470</v>
+        <v>117664452</v>
       </c>
       <c r="B4" t="n">
-        <v>97754</v>
+        <v>56500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,34 +896,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223591</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762765</v>
+        <v>762768</v>
       </c>
       <c r="R4" t="n">
-        <v>7308648</v>
+        <v>7308676</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -979,13 +962,17 @@
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,7 +984,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1007,7 +994,7 @@
         <v>117664457</v>
       </c>
       <c r="B5" t="n">
-        <v>56499</v>
+        <v>56500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1115,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117664452</v>
+        <v>117666782</v>
       </c>
       <c r="B6" t="n">
-        <v>56499</v>
+        <v>57170</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,31 +1114,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100011</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1159,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>762768</v>
+        <v>762791</v>
       </c>
       <c r="R6" t="n">
-        <v>7308676</v>
+        <v>7308597</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1192,14 +1187,19 @@
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>spillning</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,12 +1214,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1229,7 +1229,7 @@
         <v>117996055</v>
       </c>
       <c r="B7" t="n">
-        <v>79597</v>
+        <v>79599</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>117996053</v>
       </c>
       <c r="B8" t="n">
-        <v>97870</v>
+        <v>97872</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 61009-2021 artfynd.xlsx
+++ b/artfynd/A 61009-2021 artfynd.xlsx
@@ -1430,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118814664</v>
+        <v>118814665</v>
       </c>
       <c r="B9" t="n">
-        <v>6267</v>
+        <v>78484</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,43 +1446,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100524</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig flatbagge</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calitys scabra</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Thunberg, 1784)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762698</v>
+        <v>762717</v>
       </c>
       <c r="R9" t="n">
-        <v>7309060</v>
+        <v>7309146</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,11 +1516,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>tallåga m citronticka</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1546,7 +1532,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118814724</v>
+        <v>118814721</v>
       </c>
       <c r="B10" t="n">
         <v>78484</v>
@@ -1586,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762688</v>
+        <v>762648</v>
       </c>
       <c r="R10" t="n">
-        <v>7309340</v>
+        <v>7309352</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,17 +1627,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Åsa Gustafsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118814672</v>
+        <v>118814662</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>78510</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1688,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762696</v>
+        <v>762703</v>
       </c>
       <c r="R11" t="n">
-        <v>7309302</v>
+        <v>7309004</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118814659</v>
+        <v>118814670</v>
       </c>
       <c r="B12" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,21 +1752,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762681</v>
+        <v>762720</v>
       </c>
       <c r="R12" t="n">
-        <v>7308904</v>
+        <v>7309225</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,11 +1822,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>död tall</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1857,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118814662</v>
+        <v>118814671</v>
       </c>
       <c r="B13" t="n">
-        <v>78510</v>
+        <v>5166</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,34 +1854,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762703</v>
+        <v>762695</v>
       </c>
       <c r="R13" t="n">
-        <v>7309004</v>
+        <v>7309296</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,6 +1929,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>död gran</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1959,10 +1950,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118814668</v>
+        <v>118814672</v>
       </c>
       <c r="B14" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,21 +1966,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>762726</v>
+        <v>762696</v>
       </c>
       <c r="R14" t="n">
-        <v>7309203</v>
+        <v>7309302</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,17 +2045,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Åsa Gustafsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118814655</v>
+        <v>118814657</v>
       </c>
       <c r="B15" t="n">
-        <v>91802</v>
+        <v>78484</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,21 +2068,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>762789</v>
+        <v>762671</v>
       </c>
       <c r="R15" t="n">
-        <v>7308743</v>
+        <v>7308858</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,10 +2154,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118814667</v>
+        <v>118814669</v>
       </c>
       <c r="B16" t="n">
-        <v>78510</v>
+        <v>78484</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,25 +2166,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2203,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>762723</v>
+        <v>762725</v>
       </c>
       <c r="R16" t="n">
-        <v>7309154</v>
+        <v>7309207</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118814671</v>
+        <v>118814654</v>
       </c>
       <c r="B17" t="n">
-        <v>5166</v>
+        <v>97848</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,39 +2272,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>219811</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>762695</v>
+        <v>762819</v>
       </c>
       <c r="R17" t="n">
-        <v>7309296</v>
+        <v>7308845</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,11 +2342,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>död gran</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2377,7 +2358,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118814665</v>
+        <v>118814724</v>
       </c>
       <c r="B18" t="n">
         <v>78484</v>
@@ -2417,10 +2398,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>762717</v>
+        <v>762688</v>
       </c>
       <c r="R18" t="n">
-        <v>7309146</v>
+        <v>7309340</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,17 +2453,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Åsa Gustafsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118814721</v>
+        <v>118814659</v>
       </c>
       <c r="B19" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,21 +2476,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2500,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>762648</v>
+        <v>762681</v>
       </c>
       <c r="R19" t="n">
-        <v>7309352</v>
+        <v>7308904</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2565,6 +2546,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>död tall</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2581,10 +2567,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118814654</v>
+        <v>118814664</v>
       </c>
       <c r="B20" t="n">
-        <v>97848</v>
+        <v>6267</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2593,38 +2579,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219811</v>
+        <v>100524</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skrovlig flatbagge</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Calitys scabra</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Thunberg, 1784)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>762819</v>
+        <v>762698</v>
       </c>
       <c r="R20" t="n">
-        <v>7308845</v>
+        <v>7309060</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,6 +2662,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>tallåga m citronticka</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2683,10 +2683,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118814670</v>
+        <v>118814668</v>
       </c>
       <c r="B21" t="n">
-        <v>78484</v>
+        <v>78518</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>762720</v>
+        <v>762726</v>
       </c>
       <c r="R21" t="n">
-        <v>7309225</v>
+        <v>7309203</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2785,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118814669</v>
+        <v>118814655</v>
       </c>
       <c r="B22" t="n">
-        <v>78484</v>
+        <v>91802</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2801,21 +2801,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>762725</v>
+        <v>762789</v>
       </c>
       <c r="R22" t="n">
-        <v>7309207</v>
+        <v>7308743</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2887,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118814657</v>
+        <v>118814667</v>
       </c>
       <c r="B23" t="n">
-        <v>78484</v>
+        <v>78510</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2899,25 +2899,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>762671</v>
+        <v>762723</v>
       </c>
       <c r="R23" t="n">
-        <v>7308858</v>
+        <v>7309154</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 61009-2021 artfynd.xlsx
+++ b/artfynd/A 61009-2021 artfynd.xlsx
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118814662</v>
+        <v>118814670</v>
       </c>
       <c r="B11" t="n">
-        <v>78510</v>
+        <v>78484</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762703</v>
+        <v>762720</v>
       </c>
       <c r="R11" t="n">
-        <v>7309004</v>
+        <v>7309225</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118814670</v>
+        <v>118814662</v>
       </c>
       <c r="B12" t="n">
-        <v>78484</v>
+        <v>78510</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1748,25 +1748,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762720</v>
+        <v>762703</v>
       </c>
       <c r="R12" t="n">
-        <v>7309225</v>
+        <v>7309004</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 61009-2021 artfynd.xlsx
+++ b/artfynd/A 61009-2021 artfynd.xlsx
@@ -1430,7 +1430,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118814665</v>
+        <v>118814724</v>
       </c>
       <c r="B9" t="n">
         <v>78484</v>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762717</v>
+        <v>762688</v>
       </c>
       <c r="R9" t="n">
-        <v>7309146</v>
+        <v>7309340</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,17 +1525,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Åsa Gustafsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118814721</v>
+        <v>118814655</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
+        <v>91802</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,21 +1548,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762648</v>
+        <v>762789</v>
       </c>
       <c r="R10" t="n">
-        <v>7309352</v>
+        <v>7308743</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,14 +1627,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Åsa Gustafsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118814670</v>
+        <v>118814721</v>
       </c>
       <c r="B11" t="n">
         <v>78484</v>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762720</v>
+        <v>762648</v>
       </c>
       <c r="R11" t="n">
-        <v>7309225</v>
+        <v>7309352</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,17 +1729,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Åsa Gustafsson, Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118814662</v>
+        <v>118814657</v>
       </c>
       <c r="B12" t="n">
-        <v>78510</v>
+        <v>78484</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1748,25 +1748,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762703</v>
+        <v>762671</v>
       </c>
       <c r="R12" t="n">
-        <v>7309004</v>
+        <v>7308858</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1838,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118814671</v>
+        <v>118814664</v>
       </c>
       <c r="B13" t="n">
-        <v>5166</v>
+        <v>6267</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1850,31 +1850,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>100524</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skrovlig flatbagge</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Calitys scabra</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Thunberg, 1784)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1883,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762695</v>
+        <v>762698</v>
       </c>
       <c r="R13" t="n">
-        <v>7309296</v>
+        <v>7309060</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1936,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>död gran</t>
+          <t>tallåga m citronticka</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1950,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118814672</v>
+        <v>118814667</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
+        <v>78510</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1962,25 +1966,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1990,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>762696</v>
+        <v>762723</v>
       </c>
       <c r="R14" t="n">
-        <v>7309302</v>
+        <v>7309154</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,14 +2049,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Åsa Gustafsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118814657</v>
+        <v>118814665</v>
       </c>
       <c r="B15" t="n">
         <v>78484</v>
@@ -2092,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>762671</v>
+        <v>762717</v>
       </c>
       <c r="R15" t="n">
-        <v>7308858</v>
+        <v>7309146</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2154,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118814669</v>
+        <v>118814672</v>
       </c>
       <c r="B16" t="n">
         <v>78484</v>
@@ -2194,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>762725</v>
+        <v>762696</v>
       </c>
       <c r="R16" t="n">
-        <v>7309207</v>
+        <v>7309302</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118814654</v>
+        <v>118814659</v>
       </c>
       <c r="B17" t="n">
-        <v>97848</v>
+        <v>79073</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2268,25 +2272,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219811</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2296,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>762819</v>
+        <v>762681</v>
       </c>
       <c r="R17" t="n">
-        <v>7308845</v>
+        <v>7308904</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,6 +2346,11 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>död tall</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2358,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118814724</v>
+        <v>118814668</v>
       </c>
       <c r="B18" t="n">
-        <v>78484</v>
+        <v>78518</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2374,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2398,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>762688</v>
+        <v>762726</v>
       </c>
       <c r="R18" t="n">
-        <v>7309340</v>
+        <v>7309203</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,17 +2462,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Åsa Gustafsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118814659</v>
+        <v>118814654</v>
       </c>
       <c r="B19" t="n">
-        <v>79073</v>
+        <v>97848</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2472,25 +2481,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>219811</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2500,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>762681</v>
+        <v>762819</v>
       </c>
       <c r="R19" t="n">
-        <v>7308904</v>
+        <v>7308845</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2546,11 +2555,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>död tall</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2567,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118814664</v>
+        <v>118814671</v>
       </c>
       <c r="B20" t="n">
-        <v>6267</v>
+        <v>5166</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2579,35 +2583,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100524</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovlig flatbagge</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calitys scabra</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Thunberg, 1784)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>762698</v>
+        <v>762695</v>
       </c>
       <c r="R20" t="n">
-        <v>7309060</v>
+        <v>7309296</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>tallåga m citronticka</t>
+          <t>död gran</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118814668</v>
+        <v>118814662</v>
       </c>
       <c r="B21" t="n">
-        <v>78518</v>
+        <v>78510</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2695,25 +2695,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>6434</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>762726</v>
+        <v>762703</v>
       </c>
       <c r="R21" t="n">
-        <v>7309203</v>
+        <v>7309004</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2785,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118814655</v>
+        <v>118814670</v>
       </c>
       <c r="B22" t="n">
-        <v>91802</v>
+        <v>78484</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2801,21 +2801,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>762789</v>
+        <v>762720</v>
       </c>
       <c r="R22" t="n">
-        <v>7308743</v>
+        <v>7309225</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2887,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118814667</v>
+        <v>118814669</v>
       </c>
       <c r="B23" t="n">
-        <v>78510</v>
+        <v>78484</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2899,25 +2899,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>762723</v>
+        <v>762725</v>
       </c>
       <c r="R23" t="n">
-        <v>7309154</v>
+        <v>7309207</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 61009-2021 artfynd.xlsx
+++ b/artfynd/A 61009-2021 artfynd.xlsx
@@ -1430,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118814724</v>
+        <v>118814654</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>97855</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,25 +1442,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>219811</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762688</v>
+        <v>762819</v>
       </c>
       <c r="R9" t="n">
-        <v>7309340</v>
+        <v>7308845</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,17 +1525,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Åsa Gustafsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118814655</v>
+        <v>118814669</v>
       </c>
       <c r="B10" t="n">
-        <v>91802</v>
+        <v>78491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,21 +1548,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762789</v>
+        <v>762725</v>
       </c>
       <c r="R10" t="n">
-        <v>7308743</v>
+        <v>7309207</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118814721</v>
+        <v>118814659</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>79080</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762648</v>
+        <v>762681</v>
       </c>
       <c r="R11" t="n">
-        <v>7309352</v>
+        <v>7308904</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,6 +1721,11 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>död tall</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1729,17 +1734,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Åsa Gustafsson, Andreas Garpebring</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118814657</v>
+        <v>118814664</v>
       </c>
       <c r="B12" t="n">
-        <v>78484</v>
+        <v>6267</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,34 +1757,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100524</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig flatbagge</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calitys scabra</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Thunberg, 1784)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762671</v>
+        <v>762698</v>
       </c>
       <c r="R12" t="n">
-        <v>7308858</v>
+        <v>7309060</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,6 +1836,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>tallåga m citronticka</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1838,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118814664</v>
+        <v>118814672</v>
       </c>
       <c r="B13" t="n">
-        <v>6267</v>
+        <v>78491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,43 +1873,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100524</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig flatbagge</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calitys scabra</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Thunberg, 1784)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762698</v>
+        <v>762696</v>
       </c>
       <c r="R13" t="n">
-        <v>7309060</v>
+        <v>7309302</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,11 +1943,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>tallåga m citronticka</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1954,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118814667</v>
+        <v>118814668</v>
       </c>
       <c r="B14" t="n">
-        <v>78510</v>
+        <v>78525</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1966,25 +1971,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>762723</v>
+        <v>762726</v>
       </c>
       <c r="R14" t="n">
-        <v>7309154</v>
+        <v>7309203</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118814665</v>
+        <v>118814670</v>
       </c>
       <c r="B15" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2096,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>762717</v>
+        <v>762720</v>
       </c>
       <c r="R15" t="n">
-        <v>7309146</v>
+        <v>7309225</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118814672</v>
+        <v>118814667</v>
       </c>
       <c r="B16" t="n">
-        <v>78484</v>
+        <v>78517</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2170,25 +2175,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>762696</v>
+        <v>762723</v>
       </c>
       <c r="R16" t="n">
-        <v>7309302</v>
+        <v>7309154</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118814659</v>
+        <v>118814724</v>
       </c>
       <c r="B17" t="n">
-        <v>79073</v>
+        <v>78491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>762681</v>
+        <v>762688</v>
       </c>
       <c r="R17" t="n">
-        <v>7308904</v>
+        <v>7309340</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,11 +2351,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>död tall</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118814668</v>
+        <v>118814662</v>
       </c>
       <c r="B18" t="n">
-        <v>78518</v>
+        <v>78517</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2379,25 +2379,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>762726</v>
+        <v>762703</v>
       </c>
       <c r="R18" t="n">
-        <v>7309203</v>
+        <v>7309004</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118814654</v>
+        <v>118814665</v>
       </c>
       <c r="B19" t="n">
-        <v>97848</v>
+        <v>78491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2481,25 +2481,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219811</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>762819</v>
+        <v>762717</v>
       </c>
       <c r="R19" t="n">
-        <v>7308845</v>
+        <v>7309146</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118814671</v>
+        <v>118814655</v>
       </c>
       <c r="B20" t="n">
-        <v>5166</v>
+        <v>91809</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2583,43 +2583,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>762695</v>
+        <v>762789</v>
       </c>
       <c r="R20" t="n">
-        <v>7309296</v>
+        <v>7308743</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2662,11 +2657,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>död gran</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2683,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118814662</v>
+        <v>118814657</v>
       </c>
       <c r="B21" t="n">
-        <v>78510</v>
+        <v>78491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2695,25 +2685,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>762703</v>
+        <v>762671</v>
       </c>
       <c r="R21" t="n">
-        <v>7309004</v>
+        <v>7308858</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2785,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118814670</v>
+        <v>118814671</v>
       </c>
       <c r="B22" t="n">
-        <v>78484</v>
+        <v>5166</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2797,38 +2787,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>762720</v>
+        <v>762695</v>
       </c>
       <c r="R22" t="n">
-        <v>7309225</v>
+        <v>7309296</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2871,6 +2866,11 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>död gran</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2887,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118814669</v>
+        <v>118814721</v>
       </c>
       <c r="B23" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>762725</v>
+        <v>762648</v>
       </c>
       <c r="R23" t="n">
-        <v>7309207</v>
+        <v>7309352</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 61009-2021 artfynd.xlsx
+++ b/artfynd/A 61009-2021 artfynd.xlsx
@@ -1430,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118814654</v>
+        <v>118814670</v>
       </c>
       <c r="B9" t="n">
-        <v>97855</v>
+        <v>78491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,25 +1442,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219811</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>762819</v>
+        <v>762720</v>
       </c>
       <c r="R9" t="n">
-        <v>7308845</v>
+        <v>7309225</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,7 +1532,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118814669</v>
+        <v>118814724</v>
       </c>
       <c r="B10" t="n">
         <v>78491</v>
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762725</v>
+        <v>762688</v>
       </c>
       <c r="R10" t="n">
-        <v>7309207</v>
+        <v>7309340</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118814659</v>
+        <v>118814654</v>
       </c>
       <c r="B11" t="n">
-        <v>79080</v>
+        <v>97855</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>219811</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762681</v>
+        <v>762819</v>
       </c>
       <c r="R11" t="n">
-        <v>7308904</v>
+        <v>7308845</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,11 +1720,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>död tall</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1857,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118814672</v>
+        <v>118814662</v>
       </c>
       <c r="B13" t="n">
-        <v>78491</v>
+        <v>78517</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1869,25 +1864,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762696</v>
+        <v>762703</v>
       </c>
       <c r="R13" t="n">
-        <v>7309302</v>
+        <v>7309004</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118814668</v>
+        <v>118814655</v>
       </c>
       <c r="B14" t="n">
-        <v>78525</v>
+        <v>91809</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>762726</v>
+        <v>762789</v>
       </c>
       <c r="R14" t="n">
-        <v>7309203</v>
+        <v>7308743</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118814670</v>
+        <v>118814668</v>
       </c>
       <c r="B15" t="n">
-        <v>78491</v>
+        <v>78525</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>762720</v>
+        <v>762726</v>
       </c>
       <c r="R15" t="n">
-        <v>7309225</v>
+        <v>7309203</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118814667</v>
+        <v>118814669</v>
       </c>
       <c r="B16" t="n">
-        <v>78517</v>
+        <v>78491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,25 +2170,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2203,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>762723</v>
+        <v>762725</v>
       </c>
       <c r="R16" t="n">
-        <v>7309154</v>
+        <v>7309207</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118814724</v>
+        <v>118814659</v>
       </c>
       <c r="B17" t="n">
-        <v>78491</v>
+        <v>79080</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>762688</v>
+        <v>762681</v>
       </c>
       <c r="R17" t="n">
-        <v>7309340</v>
+        <v>7308904</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,6 +2346,11 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>död tall</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118814662</v>
+        <v>118814665</v>
       </c>
       <c r="B18" t="n">
-        <v>78517</v>
+        <v>78491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2379,25 +2379,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>762703</v>
+        <v>762717</v>
       </c>
       <c r="R18" t="n">
-        <v>7309004</v>
+        <v>7309146</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118814665</v>
+        <v>118814667</v>
       </c>
       <c r="B19" t="n">
-        <v>78491</v>
+        <v>78517</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2481,25 +2481,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>762717</v>
+        <v>762723</v>
       </c>
       <c r="R19" t="n">
-        <v>7309146</v>
+        <v>7309154</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118814655</v>
+        <v>118814721</v>
       </c>
       <c r="B20" t="n">
-        <v>91809</v>
+        <v>78491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,21 +2587,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>762789</v>
+        <v>762648</v>
       </c>
       <c r="R20" t="n">
-        <v>7308743</v>
+        <v>7309352</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2673,7 +2673,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118814657</v>
+        <v>118814672</v>
       </c>
       <c r="B21" t="n">
         <v>78491</v>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>762671</v>
+        <v>762696</v>
       </c>
       <c r="R21" t="n">
-        <v>7308858</v>
+        <v>7309302</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118814671</v>
+        <v>118814657</v>
       </c>
       <c r="B22" t="n">
-        <v>5166</v>
+        <v>78491</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2787,43 +2787,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>762695</v>
+        <v>762671</v>
       </c>
       <c r="R22" t="n">
-        <v>7309296</v>
+        <v>7308858</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,11 +2861,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>död gran</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2887,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118814721</v>
+        <v>118814671</v>
       </c>
       <c r="B23" t="n">
-        <v>78491</v>
+        <v>5166</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2899,38 +2889,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>762648</v>
+        <v>762695</v>
       </c>
       <c r="R23" t="n">
-        <v>7309352</v>
+        <v>7309296</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,6 +2968,11 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>död gran</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 61009-2021 artfynd.xlsx
+++ b/artfynd/A 61009-2021 artfynd.xlsx
@@ -900,11 +900,11 @@
         <v>117666782</v>
       </c>
       <c r="B4" t="n">
-        <v>57170</v>
+        <v>57264</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/artfynd/A 61009-2021 artfynd.xlsx
+++ b/artfynd/A 61009-2021 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>117666782</v>
       </c>
       <c r="B4" t="n">
-        <v>57358</v>
+        <v>57361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 61009-2021 artfynd.xlsx
+++ b/artfynd/A 61009-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117664457</v>
+        <v>118814668</v>
       </c>
       <c r="B2" t="n">
-        <v>56500</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762798</v>
+        <v>762726</v>
       </c>
       <c r="R2" t="n">
-        <v>7308440</v>
+        <v>7309203</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>spillning</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,55 +760,49 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117664452</v>
+        <v>117663042</v>
       </c>
       <c r="B3" t="n">
-        <v>56500</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762768</v>
+        <v>762726</v>
       </c>
       <c r="R3" t="n">
-        <v>7308676</v>
+        <v>7308406</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -868,17 +848,13 @@
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,22 +866,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117666782</v>
+        <v>117664449</v>
       </c>
       <c r="B4" t="n">
-        <v>57361</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,46 +884,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100011</v>
+        <v>3242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762791</v>
+        <v>762801</v>
       </c>
       <c r="R4" t="n">
-        <v>7308597</v>
+        <v>7308448</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -982,19 +941,9 @@
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,49 +958,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117664470</v>
+        <v>118814719</v>
       </c>
       <c r="B5" t="n">
-        <v>97756</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223591</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,13 +1005,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762765</v>
+        <v>762589</v>
       </c>
       <c r="R5" t="n">
-        <v>7308648</v>
+        <v>7309400</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,12 +1035,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,34 +1049,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117664449</v>
+        <v>118814653</v>
       </c>
       <c r="B6" t="n">
-        <v>90427</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1164,13 +1102,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>762801</v>
+        <v>762883</v>
       </c>
       <c r="R6" t="n">
-        <v>7308448</v>
+        <v>7309004</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,12 +1132,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,62 +1152,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117996053</v>
+        <v>117664462</v>
       </c>
       <c r="B7" t="n">
-        <v>97880</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>762933</v>
+        <v>762702</v>
       </c>
       <c r="R7" t="n">
-        <v>7308841</v>
+        <v>7308444</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1296,12 +1229,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,53 +1261,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117996055</v>
+        <v>118814655</v>
       </c>
       <c r="B8" t="n">
-        <v>79601</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fällfors, Nb</t>
+          <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>762931</v>
+        <v>762789</v>
       </c>
       <c r="R8" t="n">
-        <v>7308827</v>
+        <v>7308743</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1398,12 +1326,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1418,12 +1346,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1433,16 +1361,11 @@
         <v>118814657</v>
       </c>
       <c r="B9" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1532,37 +1455,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118814655</v>
+        <v>118814665</v>
       </c>
       <c r="B10" t="n">
-        <v>91814</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1572,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762789</v>
+        <v>762717</v>
       </c>
       <c r="R10" t="n">
-        <v>7308743</v>
+        <v>7309146</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,16 +1555,11 @@
         <v>118814669</v>
       </c>
       <c r="B11" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1736,19 +1649,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118814672</v>
+        <v>118814670</v>
       </c>
       <c r="B12" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1776,10 +1684,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762696</v>
+        <v>762720</v>
       </c>
       <c r="R12" t="n">
-        <v>7309302</v>
+        <v>7309225</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1838,19 +1746,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118814721</v>
+        <v>118814672</v>
       </c>
       <c r="B13" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1878,10 +1781,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>762648</v>
+        <v>762696</v>
       </c>
       <c r="R13" t="n">
-        <v>7309352</v>
+        <v>7309302</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,37 +1843,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118814667</v>
+        <v>118814673</v>
       </c>
       <c r="B14" t="n">
-        <v>78519</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1980,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>762723</v>
+        <v>762705</v>
       </c>
       <c r="R14" t="n">
-        <v>7309154</v>
+        <v>7309322</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,37 +1940,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118814654</v>
+        <v>118814721</v>
       </c>
       <c r="B15" t="n">
-        <v>97860</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219811</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2082,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>762819</v>
+        <v>762648</v>
       </c>
       <c r="R15" t="n">
-        <v>7308845</v>
+        <v>7309352</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2144,37 +2037,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118814659</v>
+        <v>118814724</v>
       </c>
       <c r="B16" t="n">
-        <v>79082</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2184,10 +2072,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>762681</v>
+        <v>762688</v>
       </c>
       <c r="R16" t="n">
-        <v>7308904</v>
+        <v>7309340</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,11 +2118,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>död tall</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2251,19 +2134,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118814670</v>
+        <v>118814725</v>
       </c>
       <c r="B17" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2291,10 +2169,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>762720</v>
+        <v>762701</v>
       </c>
       <c r="R17" t="n">
-        <v>7309225</v>
+        <v>7309339</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2353,37 +2231,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118814724</v>
+        <v>118814662</v>
       </c>
       <c r="B18" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2393,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>762688</v>
+        <v>762703</v>
       </c>
       <c r="R18" t="n">
-        <v>7309340</v>
+        <v>7309004</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,37 +2328,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118814665</v>
+        <v>118814667</v>
       </c>
       <c r="B19" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2495,10 +2363,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>762717</v>
+        <v>762723</v>
       </c>
       <c r="R19" t="n">
-        <v>7309146</v>
+        <v>7309154</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,53 +2425,55 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118814662</v>
+        <v>117659873</v>
       </c>
       <c r="B20" t="n">
-        <v>78519</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>762703</v>
+        <v>762765</v>
       </c>
       <c r="R20" t="n">
-        <v>7309004</v>
+        <v>7308409</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2627,12 +2497,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2641,71 +2511,67 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118814668</v>
+        <v>117996037</v>
       </c>
       <c r="B21" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>762726</v>
+        <v>762933</v>
       </c>
       <c r="R21" t="n">
-        <v>7309203</v>
+        <v>7308827</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2729,12 +2595,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2749,27 +2615,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118814671</v>
+        <v>117996055</v>
       </c>
       <c r="B22" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2777,42 +2638,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fällforsberget, Nb</t>
+          <t>Fällfors, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>762695</v>
+        <v>762931</v>
       </c>
       <c r="R22" t="n">
-        <v>7309296</v>
+        <v>7308827</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2836,12 +2692,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2852,36 +2708,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>död gran</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118814664</v>
+        <v>117666782</v>
       </c>
       <c r="B23" t="n">
-        <v>6267</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2889,21 +2735,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100524</v>
+        <v>100011</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovlig flatbagge</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calitys scabra</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Thunberg, 1784)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2911,24 +2757,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fällforsberget, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>762698</v>
+        <v>762791</v>
       </c>
       <c r="R23" t="n">
-        <v>7309060</v>
+        <v>7308597</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2952,12 +2801,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2968,24 +2827,1340 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>tallåga m citronticka</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>118814664</v>
+      </c>
+      <c r="B24" t="n">
+        <v>6284</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100524</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skrovlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Calitys scabra</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Thunberg, 1784)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>762698</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7309060</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>tallåga m citronticka</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>Andreas Garpebring</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118814671</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>762695</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7309296</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>död gran</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>117996049</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Fällfors, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>762954</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7308830</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>118814654</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>762819</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7308845</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>117995604</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>762955</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7308825</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>117995608</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>762928</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7308793</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>117996053</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fällfors, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>762933</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7308841</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>118156952</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>762967</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7308839</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>118156977</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>762953</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7308823</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>117664470</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>762765</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7308648</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>117660300</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>762720</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7308402</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>118814659</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>762681</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7308904</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>död tall</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>117661399</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Fällforsberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>762825</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7308431</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61009-2021 artfynd.xlsx
+++ b/artfynd/A 61009-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118814668</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117663042</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664449</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118814719</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118814653</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664462</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118814655</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118814657</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118814665</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118814669</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118814670</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118814672</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1937,6 +2002,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118814673</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2034,6 +2104,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118814721</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2131,6 +2206,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118814724</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2228,6 +2308,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118814725</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2325,6 +2410,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118814662</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2422,6 +2512,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118814667</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2527,6 +2622,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117659873</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2624,6 +2724,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996037</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2721,6 +2826,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996055</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2840,6 +2950,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117666782</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2951,6 +3066,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118814664</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3058,6 +3178,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118814671</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3155,6 +3280,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996049</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3252,6 +3382,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118814654</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3349,6 +3484,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117995604</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3446,6 +3586,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117995608</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3543,6 +3688,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117996053</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3649,6 +3799,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118156952</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3755,6 +3910,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118156977</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3853,6 +4013,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117664470</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3958,6 +4123,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117660300</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4060,6 +4230,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118814659</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4161,8 +4336,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117661399</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>